--- a/根管充填長度_20260904.xlsx
+++ b/根管充填長度_20260904.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yunghsin/Desktop/根管充填長度/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\小專題\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B23D995-14CA-7645-90F8-D24C2AC5BA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1416FF5-21A6-4359-BBD8-39A3FD05DEAD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14140" yWindow="660" windowWidth="15260" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14145" yWindow="660" windowWidth="15255" windowHeight="18465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="資料填寫" sheetId="1" r:id="rId1"/>
@@ -18,22 +18,11 @@
     <sheet name="填寫說明" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="80">
   <si>
     <t>根管充填長度分析－醫師資料填寫表</t>
   </si>
@@ -300,15 +289,9 @@
     <t>032.jpg</t>
   </si>
   <si>
-    <t>033.jpg</t>
-  </si>
-  <si>
     <t>034.jpg</t>
   </si>
   <si>
-    <t>035.jpg</t>
-  </si>
-  <si>
     <t>036.jpg</t>
   </si>
   <si>
@@ -358,9 +341,6 @@
   </si>
   <si>
     <t>052.jpg</t>
-  </si>
-  <si>
-    <t>053.jpg</t>
   </si>
   <si>
     <t>054.jpg</t>
@@ -883,7 +863,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RootCanalFillingDataTable" displayName="RootCanalFillingDataTable" ref="A4:D124" headerRowDxfId="5" totalsRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RootCanalFillingDataTable" displayName="RootCanalFillingDataTable" ref="A4:D121" headerRowDxfId="5" totalsRowDxfId="4">
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="圖片檔名" dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{AE52ADC9-4E24-477C-9EF4-5444F0E87BDF}" name="填充物長度(mm)" dataDxfId="2" dataCellStyle="Normal"/>
@@ -1043,15 +1023,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA124"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="22" customHeight="1"/>
+  <dimension ref="A1:BA121"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="21.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13" style="22" customWidth="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="49.6640625" style="18" customWidth="1"/>
-    <col min="5" max="53" width="8.83203125" style="19"/>
-    <col min="54" max="16384" width="8.83203125" style="1"/>
+    <col min="4" max="4" width="49.625" style="18" customWidth="1"/>
+    <col min="5" max="53" width="8.875" style="19"/>
+    <col min="54" max="16384" width="8.875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
@@ -1062,7 +1042,7 @@
       <c r="C1" s="23"/>
       <c r="D1" s="23"/>
     </row>
-    <row r="2" spans="1:4" ht="27.25" customHeight="1">
+    <row r="2" spans="1:4" ht="27.2" customHeight="1">
       <c r="A2" s="24" t="s">
         <v>19</v>
       </c>
@@ -1070,7 +1050,7 @@
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
     </row>
-    <row r="3" spans="1:4" ht="27.25" customHeight="1">
+    <row r="3" spans="1:4" ht="27.2" customHeight="1">
       <c r="A3" s="26" t="s">
         <v>17</v>
       </c>
@@ -1092,7 +1072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="22" customHeight="1">
+    <row r="5" spans="1:4" ht="21.95" customHeight="1">
       <c r="A5" s="21" t="s">
         <v>23</v>
       </c>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="D5" s="17"/>
     </row>
-    <row r="6" spans="1:4" ht="22" customHeight="1">
+    <row r="6" spans="1:4" ht="21.95" customHeight="1">
       <c r="A6" s="21" t="s">
         <v>24</v>
       </c>
@@ -1118,7 +1098,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="22" customHeight="1">
+    <row r="7" spans="1:4" ht="21.95" customHeight="1">
       <c r="A7" s="21" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1110,7 @@
       </c>
       <c r="D7" s="17"/>
     </row>
-    <row r="8" spans="1:4" ht="22" customHeight="1">
+    <row r="8" spans="1:4" ht="21.95" customHeight="1">
       <c r="A8" s="21" t="s">
         <v>27</v>
       </c>
@@ -1142,7 +1122,7 @@
       </c>
       <c r="D8" s="17"/>
     </row>
-    <row r="9" spans="1:4" ht="22" customHeight="1">
+    <row r="9" spans="1:4" ht="21.95" customHeight="1">
       <c r="A9" s="21" t="s">
         <v>28</v>
       </c>
@@ -1154,7 +1134,7 @@
       </c>
       <c r="D9" s="17"/>
     </row>
-    <row r="10" spans="1:4" ht="22" customHeight="1">
+    <row r="10" spans="1:4" ht="21.95" customHeight="1">
       <c r="A10" s="21" t="s">
         <v>30</v>
       </c>
@@ -1166,7 +1146,7 @@
       </c>
       <c r="D10" s="17"/>
     </row>
-    <row r="11" spans="1:4" ht="22" customHeight="1">
+    <row r="11" spans="1:4" ht="21.95" customHeight="1">
       <c r="A11" s="21" t="s">
         <v>31</v>
       </c>
@@ -1180,7 +1160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="22" customHeight="1">
+    <row r="12" spans="1:4" ht="21.95" customHeight="1">
       <c r="A12" s="21" t="s">
         <v>33</v>
       </c>
@@ -1192,7 +1172,7 @@
       </c>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:4" ht="22" customHeight="1">
+    <row r="13" spans="1:4" ht="21.95" customHeight="1">
       <c r="A13" s="21" t="s">
         <v>34</v>
       </c>
@@ -1204,7 +1184,7 @@
       </c>
       <c r="D13" s="17"/>
     </row>
-    <row r="14" spans="1:4" ht="22" customHeight="1">
+    <row r="14" spans="1:4" ht="21.95" customHeight="1">
       <c r="A14" s="21" t="s">
         <v>35</v>
       </c>
@@ -1216,7 +1196,7 @@
       </c>
       <c r="D14" s="17"/>
     </row>
-    <row r="15" spans="1:4" ht="22" customHeight="1">
+    <row r="15" spans="1:4" ht="21.95" customHeight="1">
       <c r="A15" s="21" t="s">
         <v>36</v>
       </c>
@@ -1228,7 +1208,7 @@
       </c>
       <c r="D15" s="17"/>
     </row>
-    <row r="16" spans="1:4" ht="22" customHeight="1">
+    <row r="16" spans="1:4" ht="21.95" customHeight="1">
       <c r="A16" s="21" t="s">
         <v>37</v>
       </c>
@@ -1240,7 +1220,7 @@
       </c>
       <c r="D16" s="17"/>
     </row>
-    <row r="17" spans="1:4" ht="22" customHeight="1">
+    <row r="17" spans="1:4" ht="21.95" customHeight="1">
       <c r="A17" s="21" t="s">
         <v>38</v>
       </c>
@@ -1252,7 +1232,7 @@
       </c>
       <c r="D17" s="17"/>
     </row>
-    <row r="18" spans="1:4" ht="22" customHeight="1">
+    <row r="18" spans="1:4" ht="21.95" customHeight="1">
       <c r="A18" s="21" t="s">
         <v>39</v>
       </c>
@@ -1264,7 +1244,7 @@
       </c>
       <c r="D18" s="17"/>
     </row>
-    <row r="19" spans="1:4" ht="22" customHeight="1">
+    <row r="19" spans="1:4" ht="21.95" customHeight="1">
       <c r="A19" s="21" t="s">
         <v>40</v>
       </c>
@@ -1276,7 +1256,7 @@
       </c>
       <c r="D19" s="17"/>
     </row>
-    <row r="20" spans="1:4" ht="22" customHeight="1">
+    <row r="20" spans="1:4" ht="21.95" customHeight="1">
       <c r="A20" s="21" t="s">
         <v>41</v>
       </c>
@@ -1288,7 +1268,7 @@
       </c>
       <c r="D20" s="17"/>
     </row>
-    <row r="21" spans="1:4" ht="22" customHeight="1">
+    <row r="21" spans="1:4" ht="21.95" customHeight="1">
       <c r="A21" s="21" t="s">
         <v>42</v>
       </c>
@@ -1300,7 +1280,7 @@
       </c>
       <c r="D21" s="17"/>
     </row>
-    <row r="22" spans="1:4" ht="22" customHeight="1">
+    <row r="22" spans="1:4" ht="21.95" customHeight="1">
       <c r="A22" s="21" t="s">
         <v>43</v>
       </c>
@@ -1312,7 +1292,7 @@
       </c>
       <c r="D22" s="17"/>
     </row>
-    <row r="23" spans="1:4" ht="22" customHeight="1">
+    <row r="23" spans="1:4" ht="21.95" customHeight="1">
       <c r="A23" s="21" t="s">
         <v>44</v>
       </c>
@@ -1324,7 +1304,7 @@
       </c>
       <c r="D23" s="17"/>
     </row>
-    <row r="24" spans="1:4" ht="22" customHeight="1">
+    <row r="24" spans="1:4" ht="21.95" customHeight="1">
       <c r="A24" s="21" t="s">
         <v>45</v>
       </c>
@@ -1336,7 +1316,7 @@
       </c>
       <c r="D24" s="17"/>
     </row>
-    <row r="25" spans="1:4" ht="22" customHeight="1">
+    <row r="25" spans="1:4" ht="21.95" customHeight="1">
       <c r="A25" s="21" t="s">
         <v>46</v>
       </c>
@@ -1348,7 +1328,7 @@
       </c>
       <c r="D25" s="17"/>
     </row>
-    <row r="26" spans="1:4" ht="22" customHeight="1">
+    <row r="26" spans="1:4" ht="21.95" customHeight="1">
       <c r="A26" s="21" t="s">
         <v>47</v>
       </c>
@@ -1360,7 +1340,7 @@
       </c>
       <c r="D26" s="17"/>
     </row>
-    <row r="27" spans="1:4" ht="22" customHeight="1">
+    <row r="27" spans="1:4" ht="21.95" customHeight="1">
       <c r="A27" s="21" t="s">
         <v>48</v>
       </c>
@@ -1372,7 +1352,7 @@
       </c>
       <c r="D27" s="17"/>
     </row>
-    <row r="28" spans="1:4" ht="22" customHeight="1">
+    <row r="28" spans="1:4" ht="21.95" customHeight="1">
       <c r="A28" s="21" t="s">
         <v>49</v>
       </c>
@@ -1384,7 +1364,7 @@
       </c>
       <c r="D28" s="17"/>
     </row>
-    <row r="29" spans="1:4" ht="22" customHeight="1">
+    <row r="29" spans="1:4" ht="21.95" customHeight="1">
       <c r="A29" s="21" t="s">
         <v>50</v>
       </c>
@@ -1396,7 +1376,7 @@
       </c>
       <c r="D29" s="17"/>
     </row>
-    <row r="30" spans="1:4" ht="22" customHeight="1">
+    <row r="30" spans="1:4" ht="21.95" customHeight="1">
       <c r="A30" s="21" t="s">
         <v>51</v>
       </c>
@@ -1408,7 +1388,7 @@
       </c>
       <c r="D30" s="17"/>
     </row>
-    <row r="31" spans="1:4" ht="22" customHeight="1">
+    <row r="31" spans="1:4" ht="21.95" customHeight="1">
       <c r="A31" s="21" t="s">
         <v>52</v>
       </c>
@@ -1420,7 +1400,7 @@
       </c>
       <c r="D31" s="17"/>
     </row>
-    <row r="32" spans="1:4" ht="22" customHeight="1">
+    <row r="32" spans="1:4" ht="21.95" customHeight="1">
       <c r="A32" s="21" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1412,7 @@
       </c>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="22" customHeight="1">
+    <row r="33" spans="1:4" ht="21.95" customHeight="1">
       <c r="A33" s="21" t="s">
         <v>54</v>
       </c>
@@ -1444,7 +1424,7 @@
       </c>
       <c r="D33" s="17"/>
     </row>
-    <row r="34" spans="1:4" ht="22" customHeight="1">
+    <row r="34" spans="1:4" ht="21.95" customHeight="1">
       <c r="A34" s="21" t="s">
         <v>55</v>
       </c>
@@ -1456,7 +1436,7 @@
       </c>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="1:4" ht="22" customHeight="1">
+    <row r="35" spans="1:4" ht="21.95" customHeight="1">
       <c r="A35" s="21" t="s">
         <v>56</v>
       </c>
@@ -1468,7 +1448,7 @@
       </c>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="22" customHeight="1">
+    <row r="36" spans="1:4" ht="21.95" customHeight="1">
       <c r="A36" s="21" t="s">
         <v>57</v>
       </c>
@@ -1480,151 +1460,151 @@
       </c>
       <c r="D36" s="17"/>
     </row>
-    <row r="37" spans="1:4" ht="22" customHeight="1">
+    <row r="37" spans="1:4" ht="21.95" customHeight="1">
       <c r="A37" s="21" t="s">
         <v>58</v>
       </c>
       <c r="B37" s="2">
-        <v>21.25</v>
+        <v>21</v>
       </c>
       <c r="C37" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4" ht="22" customHeight="1">
+    <row r="38" spans="1:4" ht="21.95" customHeight="1">
       <c r="A38" s="21" t="s">
         <v>59</v>
       </c>
       <c r="B38" s="2">
-        <v>21</v>
+        <v>20.25</v>
       </c>
       <c r="C38" s="3">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D38" s="17"/>
     </row>
-    <row r="39" spans="1:4" ht="22" customHeight="1">
+    <row r="39" spans="1:4" ht="21.95" customHeight="1">
       <c r="A39" s="21" t="s">
         <v>60</v>
       </c>
       <c r="B39" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="C39" s="3">
         <v>21</v>
       </c>
-      <c r="C39" s="3">
-        <v>12</v>
-      </c>
       <c r="D39" s="17"/>
     </row>
-    <row r="40" spans="1:4" ht="22" customHeight="1">
+    <row r="40" spans="1:4" ht="21.95" customHeight="1">
       <c r="A40" s="21" t="s">
         <v>61</v>
       </c>
       <c r="B40" s="2">
-        <v>20.25</v>
+        <v>19.5</v>
       </c>
       <c r="C40" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D40" s="17"/>
     </row>
-    <row r="41" spans="1:4" ht="22" customHeight="1">
+    <row r="41" spans="1:4" ht="21.95" customHeight="1">
       <c r="A41" s="21" t="s">
         <v>62</v>
       </c>
       <c r="B41" s="2">
-        <v>21.5</v>
+        <v>25</v>
       </c>
       <c r="C41" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D41" s="17"/>
     </row>
-    <row r="42" spans="1:4" ht="22" customHeight="1">
+    <row r="42" spans="1:4" ht="21.95" customHeight="1">
       <c r="A42" s="21" t="s">
         <v>63</v>
       </c>
       <c r="B42" s="2">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="C42" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42" s="17"/>
     </row>
-    <row r="43" spans="1:4" ht="22" customHeight="1">
+    <row r="43" spans="1:4" ht="21.95" customHeight="1">
       <c r="A43" s="21" t="s">
         <v>64</v>
       </c>
       <c r="B43" s="2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C43" s="3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D43" s="17"/>
     </row>
-    <row r="44" spans="1:4" ht="22" customHeight="1">
+    <row r="44" spans="1:4" ht="21.95" customHeight="1">
       <c r="A44" s="21" t="s">
         <v>65</v>
       </c>
       <c r="B44" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C44" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D44" s="17"/>
     </row>
-    <row r="45" spans="1:4" ht="22" customHeight="1">
+    <row r="45" spans="1:4" ht="21.95" customHeight="1">
       <c r="A45" s="21" t="s">
         <v>66</v>
       </c>
       <c r="B45" s="2">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="C45" s="3">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D45" s="17"/>
     </row>
-    <row r="46" spans="1:4" ht="22" customHeight="1">
+    <row r="46" spans="1:4" ht="21.95" customHeight="1">
       <c r="A46" s="21" t="s">
         <v>67</v>
       </c>
       <c r="B46" s="2">
-        <v>21</v>
+        <v>19.25</v>
       </c>
       <c r="C46" s="3">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D46" s="17"/>
     </row>
-    <row r="47" spans="1:4" ht="22" customHeight="1">
+    <row r="47" spans="1:4" ht="21.95" customHeight="1">
       <c r="A47" s="21" t="s">
         <v>68</v>
       </c>
       <c r="B47" s="2">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="C47" s="3">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D47" s="17"/>
     </row>
-    <row r="48" spans="1:4" ht="22" customHeight="1">
+    <row r="48" spans="1:4" ht="21.95" customHeight="1">
       <c r="A48" s="21" t="s">
         <v>69</v>
       </c>
       <c r="B48" s="2">
-        <v>19.25</v>
+        <v>20</v>
       </c>
       <c r="C48" s="3">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D48" s="17"/>
     </row>
-    <row r="49" spans="1:4" ht="22" customHeight="1">
+    <row r="49" spans="1:4" ht="21.95" customHeight="1">
       <c r="A49" s="21" t="s">
         <v>70</v>
       </c>
@@ -1632,533 +1612,497 @@
         <v>20</v>
       </c>
       <c r="C49" s="3">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D49" s="17"/>
     </row>
-    <row r="50" spans="1:4" ht="22" customHeight="1">
+    <row r="50" spans="1:4" ht="21.95" customHeight="1">
       <c r="A50" s="21" t="s">
         <v>71</v>
       </c>
       <c r="B50" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C50" s="3">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="D50" s="17"/>
     </row>
-    <row r="51" spans="1:4" ht="22" customHeight="1">
+    <row r="51" spans="1:4" ht="21.95" customHeight="1">
       <c r="A51" s="21" t="s">
         <v>72</v>
       </c>
       <c r="B51" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C51" s="3">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D51" s="17"/>
     </row>
-    <row r="52" spans="1:4" ht="22" customHeight="1">
+    <row r="52" spans="1:4" ht="21.95" customHeight="1">
       <c r="A52" s="21" t="s">
         <v>73</v>
       </c>
       <c r="B52" s="2">
+        <v>23</v>
+      </c>
+      <c r="C52" s="3">
         <v>22</v>
       </c>
-      <c r="C52" s="3">
-        <v>11</v>
-      </c>
       <c r="D52" s="17"/>
     </row>
-    <row r="53" spans="1:4" ht="22" customHeight="1">
+    <row r="53" spans="1:4" ht="21.95" customHeight="1">
       <c r="A53" s="21" t="s">
         <v>74</v>
       </c>
       <c r="B53" s="2">
-        <v>22</v>
+        <v>21.75</v>
       </c>
       <c r="C53" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D53" s="17"/>
     </row>
-    <row r="54" spans="1:4" ht="22" customHeight="1">
+    <row r="54" spans="1:4" ht="21.95" customHeight="1">
       <c r="A54" s="21" t="s">
         <v>75</v>
       </c>
       <c r="B54" s="2">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="C54" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D54" s="17"/>
     </row>
-    <row r="55" spans="1:4" ht="22" customHeight="1">
+    <row r="55" spans="1:4" ht="21.95" customHeight="1">
       <c r="A55" s="21" t="s">
         <v>76</v>
       </c>
       <c r="B55" s="2">
-        <v>21.75</v>
+        <v>19.2</v>
       </c>
       <c r="C55" s="3">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D55" s="17"/>
     </row>
-    <row r="56" spans="1:4" ht="22" customHeight="1">
+    <row r="56" spans="1:4" ht="21.95" customHeight="1">
       <c r="A56" s="21" t="s">
         <v>77</v>
       </c>
       <c r="B56" s="2">
-        <v>21.5</v>
+        <v>17.5</v>
       </c>
       <c r="C56" s="3">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D56" s="17"/>
     </row>
-    <row r="57" spans="1:4" ht="22" customHeight="1">
+    <row r="57" spans="1:4" ht="21.95" customHeight="1">
       <c r="A57" s="21" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="2">
-        <v>20.5</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="C57" s="3">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D57" s="17"/>
     </row>
-    <row r="58" spans="1:4" ht="22" customHeight="1">
+    <row r="58" spans="1:4" ht="21.95" customHeight="1">
       <c r="A58" s="21" t="s">
         <v>79</v>
       </c>
       <c r="B58" s="2">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="C58" s="3">
-        <v>32</v>
-      </c>
-      <c r="D58" s="17"/>
-    </row>
-    <row r="59" spans="1:4" ht="22" customHeight="1">
-      <c r="A59" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B59" s="2">
-        <v>17.5</v>
-      </c>
-      <c r="C59" s="3">
-        <v>31</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A59" s="21"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="3"/>
       <c r="D59" s="17"/>
     </row>
-    <row r="60" spans="1:4" ht="22" customHeight="1">
-      <c r="A60" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="2">
-        <v>18.399999999999999</v>
-      </c>
-      <c r="C60" s="3">
-        <v>41</v>
-      </c>
+    <row r="60" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A60" s="21"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="3"/>
       <c r="D60" s="17"/>
     </row>
-    <row r="61" spans="1:4" ht="22" customHeight="1">
-      <c r="A61" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B61" s="2">
-        <v>19</v>
-      </c>
-      <c r="C61" s="3">
-        <v>42</v>
-      </c>
-      <c r="D61" s="17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="22" customHeight="1">
+    <row r="61" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A61" s="21"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="17"/>
+    </row>
+    <row r="62" spans="1:4" ht="21.95" customHeight="1">
       <c r="A62" s="21"/>
       <c r="B62" s="2"/>
       <c r="C62" s="3"/>
       <c r="D62" s="17"/>
     </row>
-    <row r="63" spans="1:4" ht="22" customHeight="1">
+    <row r="63" spans="1:4" ht="21.95" customHeight="1">
       <c r="A63" s="21"/>
       <c r="B63" s="2"/>
       <c r="C63" s="3"/>
       <c r="D63" s="17"/>
     </row>
-    <row r="64" spans="1:4" ht="22" customHeight="1">
+    <row r="64" spans="1:4" ht="21.95" customHeight="1">
       <c r="A64" s="21"/>
       <c r="B64" s="2"/>
       <c r="C64" s="3"/>
       <c r="D64" s="17"/>
     </row>
-    <row r="65" spans="1:4" ht="22" customHeight="1">
+    <row r="65" spans="1:4" ht="21.95" customHeight="1">
       <c r="A65" s="21"/>
       <c r="B65" s="2"/>
       <c r="C65" s="3"/>
       <c r="D65" s="17"/>
     </row>
-    <row r="66" spans="1:4" ht="22" customHeight="1">
+    <row r="66" spans="1:4" ht="21.95" customHeight="1">
       <c r="A66" s="21"/>
       <c r="B66" s="2"/>
       <c r="C66" s="3"/>
       <c r="D66" s="17"/>
     </row>
-    <row r="67" spans="1:4" ht="22" customHeight="1">
+    <row r="67" spans="1:4" ht="21.95" customHeight="1">
       <c r="A67" s="21"/>
       <c r="B67" s="2"/>
       <c r="C67" s="3"/>
       <c r="D67" s="17"/>
     </row>
-    <row r="68" spans="1:4" ht="22" customHeight="1">
+    <row r="68" spans="1:4" ht="21.95" customHeight="1">
       <c r="A68" s="21"/>
       <c r="B68" s="2"/>
       <c r="C68" s="3"/>
       <c r="D68" s="17"/>
     </row>
-    <row r="69" spans="1:4" ht="22" customHeight="1">
+    <row r="69" spans="1:4" ht="21.95" customHeight="1">
       <c r="A69" s="21"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
       <c r="D69" s="17"/>
     </row>
-    <row r="70" spans="1:4" ht="22" customHeight="1">
+    <row r="70" spans="1:4" ht="21.95" customHeight="1">
       <c r="A70" s="21"/>
       <c r="B70" s="2"/>
       <c r="C70" s="3"/>
       <c r="D70" s="17"/>
     </row>
-    <row r="71" spans="1:4" ht="22" customHeight="1">
+    <row r="71" spans="1:4" ht="21.95" customHeight="1">
       <c r="A71" s="21"/>
       <c r="B71" s="2"/>
       <c r="C71" s="3"/>
       <c r="D71" s="17"/>
     </row>
-    <row r="72" spans="1:4" ht="22" customHeight="1">
+    <row r="72" spans="1:4" ht="21.95" customHeight="1">
       <c r="A72" s="21"/>
       <c r="B72" s="2"/>
       <c r="C72" s="3"/>
       <c r="D72" s="17"/>
     </row>
-    <row r="73" spans="1:4" ht="22" customHeight="1">
+    <row r="73" spans="1:4" ht="21.95" customHeight="1">
       <c r="A73" s="21"/>
       <c r="B73" s="2"/>
       <c r="C73" s="3"/>
       <c r="D73" s="17"/>
     </row>
-    <row r="74" spans="1:4" ht="22" customHeight="1">
+    <row r="74" spans="1:4" ht="21.95" customHeight="1">
       <c r="A74" s="21"/>
       <c r="B74" s="2"/>
       <c r="C74" s="3"/>
       <c r="D74" s="17"/>
     </row>
-    <row r="75" spans="1:4" ht="22" customHeight="1">
+    <row r="75" spans="1:4" ht="21.95" customHeight="1">
       <c r="A75" s="21"/>
       <c r="B75" s="2"/>
       <c r="C75" s="3"/>
       <c r="D75" s="17"/>
     </row>
-    <row r="76" spans="1:4" ht="22" customHeight="1">
+    <row r="76" spans="1:4" ht="21.95" customHeight="1">
       <c r="A76" s="21"/>
       <c r="B76" s="2"/>
       <c r="C76" s="3"/>
       <c r="D76" s="17"/>
     </row>
-    <row r="77" spans="1:4" ht="22" customHeight="1">
+    <row r="77" spans="1:4" ht="21.95" customHeight="1">
       <c r="A77" s="21"/>
       <c r="B77" s="2"/>
       <c r="C77" s="3"/>
       <c r="D77" s="17"/>
     </row>
-    <row r="78" spans="1:4" ht="22" customHeight="1">
+    <row r="78" spans="1:4" ht="21.95" customHeight="1">
       <c r="A78" s="21"/>
       <c r="B78" s="2"/>
       <c r="C78" s="3"/>
       <c r="D78" s="17"/>
     </row>
-    <row r="79" spans="1:4" ht="22" customHeight="1">
+    <row r="79" spans="1:4" ht="21.95" customHeight="1">
       <c r="A79" s="21"/>
       <c r="B79" s="2"/>
       <c r="C79" s="3"/>
       <c r="D79" s="17"/>
     </row>
-    <row r="80" spans="1:4" ht="22" customHeight="1">
+    <row r="80" spans="1:4" ht="21.95" customHeight="1">
       <c r="A80" s="21"/>
       <c r="B80" s="2"/>
       <c r="C80" s="3"/>
       <c r="D80" s="17"/>
     </row>
-    <row r="81" spans="1:4" ht="22" customHeight="1">
+    <row r="81" spans="1:4" ht="21.95" customHeight="1">
       <c r="A81" s="21"/>
       <c r="B81" s="2"/>
       <c r="C81" s="3"/>
       <c r="D81" s="17"/>
     </row>
-    <row r="82" spans="1:4" ht="22" customHeight="1">
+    <row r="82" spans="1:4" ht="21.95" customHeight="1">
       <c r="A82" s="21"/>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
       <c r="D82" s="17"/>
     </row>
-    <row r="83" spans="1:4" ht="22" customHeight="1">
+    <row r="83" spans="1:4" ht="21.95" customHeight="1">
       <c r="A83" s="21"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
       <c r="D83" s="17"/>
     </row>
-    <row r="84" spans="1:4" ht="22" customHeight="1">
+    <row r="84" spans="1:4" ht="21.95" customHeight="1">
       <c r="A84" s="21"/>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
       <c r="D84" s="17"/>
     </row>
-    <row r="85" spans="1:4" ht="22" customHeight="1">
+    <row r="85" spans="1:4" ht="21.95" customHeight="1">
       <c r="A85" s="21"/>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
       <c r="D85" s="17"/>
     </row>
-    <row r="86" spans="1:4" ht="22" customHeight="1">
+    <row r="86" spans="1:4" ht="21.95" customHeight="1">
       <c r="A86" s="21"/>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
       <c r="D86" s="17"/>
     </row>
-    <row r="87" spans="1:4" ht="22" customHeight="1">
+    <row r="87" spans="1:4" ht="21.95" customHeight="1">
       <c r="A87" s="21"/>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
       <c r="D87" s="17"/>
     </row>
-    <row r="88" spans="1:4" ht="22" customHeight="1">
+    <row r="88" spans="1:4" ht="21.95" customHeight="1">
       <c r="A88" s="21"/>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
       <c r="D88" s="17"/>
     </row>
-    <row r="89" spans="1:4" ht="22" customHeight="1">
+    <row r="89" spans="1:4" ht="21.95" customHeight="1">
       <c r="A89" s="21"/>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
       <c r="D89" s="17"/>
     </row>
-    <row r="90" spans="1:4" ht="22" customHeight="1">
+    <row r="90" spans="1:4" ht="21.95" customHeight="1">
       <c r="A90" s="21"/>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
       <c r="D90" s="17"/>
     </row>
-    <row r="91" spans="1:4" ht="22" customHeight="1">
+    <row r="91" spans="1:4" ht="21.95" customHeight="1">
       <c r="A91" s="21"/>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
       <c r="D91" s="17"/>
     </row>
-    <row r="92" spans="1:4" ht="22" customHeight="1">
+    <row r="92" spans="1:4" ht="21.95" customHeight="1">
       <c r="A92" s="21"/>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
       <c r="D92" s="17"/>
     </row>
-    <row r="93" spans="1:4" ht="22" customHeight="1">
+    <row r="93" spans="1:4" ht="21.95" customHeight="1">
       <c r="A93" s="21"/>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
       <c r="D93" s="17"/>
     </row>
-    <row r="94" spans="1:4" ht="22" customHeight="1">
+    <row r="94" spans="1:4" ht="21.95" customHeight="1">
       <c r="A94" s="21"/>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
       <c r="D94" s="17"/>
     </row>
-    <row r="95" spans="1:4" ht="22" customHeight="1">
+    <row r="95" spans="1:4" ht="21.95" customHeight="1">
       <c r="A95" s="21"/>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
       <c r="D95" s="17"/>
     </row>
-    <row r="96" spans="1:4" ht="22" customHeight="1">
+    <row r="96" spans="1:4" ht="21.95" customHeight="1">
       <c r="A96" s="21"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
       <c r="D96" s="17"/>
     </row>
-    <row r="97" spans="1:4" ht="22" customHeight="1">
+    <row r="97" spans="1:4" ht="21.95" customHeight="1">
       <c r="A97" s="21"/>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
       <c r="D97" s="17"/>
     </row>
-    <row r="98" spans="1:4" ht="22" customHeight="1">
+    <row r="98" spans="1:4" ht="21.95" customHeight="1">
       <c r="A98" s="21"/>
       <c r="B98" s="2"/>
       <c r="C98" s="3"/>
       <c r="D98" s="17"/>
     </row>
-    <row r="99" spans="1:4" ht="22" customHeight="1">
+    <row r="99" spans="1:4" ht="21.95" customHeight="1">
       <c r="A99" s="21"/>
       <c r="B99" s="2"/>
       <c r="C99" s="3"/>
       <c r="D99" s="17"/>
     </row>
-    <row r="100" spans="1:4" ht="22" customHeight="1">
+    <row r="100" spans="1:4" ht="21.95" customHeight="1">
       <c r="A100" s="21"/>
       <c r="B100" s="2"/>
       <c r="C100" s="3"/>
       <c r="D100" s="17"/>
     </row>
-    <row r="101" spans="1:4" ht="22" customHeight="1">
+    <row r="101" spans="1:4" ht="21.95" customHeight="1">
       <c r="A101" s="21"/>
       <c r="B101" s="2"/>
       <c r="C101" s="3"/>
       <c r="D101" s="17"/>
     </row>
-    <row r="102" spans="1:4" ht="22" customHeight="1">
+    <row r="102" spans="1:4" ht="21.95" customHeight="1">
       <c r="A102" s="21"/>
       <c r="B102" s="2"/>
       <c r="C102" s="3"/>
       <c r="D102" s="17"/>
     </row>
-    <row r="103" spans="1:4" ht="22" customHeight="1">
+    <row r="103" spans="1:4" ht="21.95" customHeight="1">
       <c r="A103" s="21"/>
       <c r="B103" s="2"/>
       <c r="C103" s="3"/>
       <c r="D103" s="17"/>
     </row>
-    <row r="104" spans="1:4" ht="22" customHeight="1">
+    <row r="104" spans="1:4" ht="21.95" customHeight="1">
       <c r="A104" s="21"/>
       <c r="B104" s="2"/>
       <c r="C104" s="3"/>
       <c r="D104" s="17"/>
     </row>
-    <row r="105" spans="1:4" ht="22" customHeight="1">
+    <row r="105" spans="1:4" ht="21.95" customHeight="1">
       <c r="A105" s="21"/>
       <c r="B105" s="2"/>
       <c r="C105" s="3"/>
       <c r="D105" s="17"/>
     </row>
-    <row r="106" spans="1:4" ht="22" customHeight="1">
+    <row r="106" spans="1:4" ht="21.95" customHeight="1">
       <c r="A106" s="21"/>
       <c r="B106" s="2"/>
       <c r="C106" s="3"/>
       <c r="D106" s="17"/>
     </row>
-    <row r="107" spans="1:4" ht="22" customHeight="1">
+    <row r="107" spans="1:4" ht="21.95" customHeight="1">
       <c r="A107" s="21"/>
       <c r="B107" s="2"/>
       <c r="C107" s="3"/>
       <c r="D107" s="17"/>
     </row>
-    <row r="108" spans="1:4" ht="22" customHeight="1">
+    <row r="108" spans="1:4" ht="21.95" customHeight="1">
       <c r="A108" s="21"/>
       <c r="B108" s="2"/>
       <c r="C108" s="3"/>
       <c r="D108" s="17"/>
     </row>
-    <row r="109" spans="1:4" ht="22" customHeight="1">
+    <row r="109" spans="1:4" ht="21.95" customHeight="1">
       <c r="A109" s="21"/>
       <c r="B109" s="2"/>
       <c r="C109" s="3"/>
       <c r="D109" s="17"/>
     </row>
-    <row r="110" spans="1:4" ht="22" customHeight="1">
+    <row r="110" spans="1:4" ht="21.95" customHeight="1">
       <c r="A110" s="21"/>
       <c r="B110" s="2"/>
       <c r="C110" s="3"/>
       <c r="D110" s="17"/>
     </row>
-    <row r="111" spans="1:4" ht="22" customHeight="1">
+    <row r="111" spans="1:4" ht="21.95" customHeight="1">
       <c r="A111" s="21"/>
       <c r="B111" s="2"/>
       <c r="C111" s="3"/>
       <c r="D111" s="17"/>
     </row>
-    <row r="112" spans="1:4" ht="22" customHeight="1">
+    <row r="112" spans="1:4" ht="21.95" customHeight="1">
       <c r="A112" s="21"/>
       <c r="B112" s="2"/>
       <c r="C112" s="3"/>
       <c r="D112" s="17"/>
     </row>
-    <row r="113" spans="1:4" ht="22" customHeight="1">
+    <row r="113" spans="1:4" ht="21.95" customHeight="1">
       <c r="A113" s="21"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
       <c r="D113" s="17"/>
     </row>
-    <row r="114" spans="1:4" ht="22" customHeight="1">
+    <row r="114" spans="1:4" ht="21.95" customHeight="1">
       <c r="A114" s="21"/>
       <c r="B114" s="2"/>
       <c r="C114" s="3"/>
       <c r="D114" s="17"/>
     </row>
-    <row r="115" spans="1:4" ht="22" customHeight="1">
+    <row r="115" spans="1:4" ht="21.95" customHeight="1">
       <c r="A115" s="21"/>
       <c r="B115" s="2"/>
       <c r="C115" s="3"/>
       <c r="D115" s="17"/>
     </row>
-    <row r="116" spans="1:4" ht="22" customHeight="1">
+    <row r="116" spans="1:4" ht="21.95" customHeight="1">
       <c r="A116" s="21"/>
       <c r="B116" s="2"/>
       <c r="C116" s="3"/>
       <c r="D116" s="17"/>
     </row>
-    <row r="117" spans="1:4" ht="22" customHeight="1">
+    <row r="117" spans="1:4" ht="21.95" customHeight="1">
       <c r="A117" s="21"/>
       <c r="B117" s="2"/>
       <c r="C117" s="3"/>
       <c r="D117" s="17"/>
     </row>
-    <row r="118" spans="1:4" ht="22" customHeight="1">
+    <row r="118" spans="1:4" ht="21.95" customHeight="1">
       <c r="A118" s="21"/>
       <c r="B118" s="2"/>
       <c r="C118" s="3"/>
       <c r="D118" s="17"/>
     </row>
-    <row r="119" spans="1:4" ht="22" customHeight="1">
+    <row r="119" spans="1:4" ht="21.95" customHeight="1">
       <c r="A119" s="21"/>
       <c r="B119" s="2"/>
       <c r="C119" s="3"/>
       <c r="D119" s="17"/>
     </row>
-    <row r="120" spans="1:4" ht="22" customHeight="1">
+    <row r="120" spans="1:4" ht="21.95" customHeight="1">
       <c r="A120" s="21"/>
       <c r="B120" s="2"/>
       <c r="C120" s="3"/>
       <c r="D120" s="17"/>
     </row>
-    <row r="121" spans="1:4" ht="22" customHeight="1">
+    <row r="121" spans="1:4" ht="21.95" customHeight="1">
       <c r="A121" s="21"/>
       <c r="B121" s="2"/>
       <c r="C121" s="3"/>
       <c r="D121" s="17"/>
-    </row>
-    <row r="122" spans="1:4" ht="22" customHeight="1">
-      <c r="A122" s="21"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="3"/>
-      <c r="D122" s="17"/>
-    </row>
-    <row r="123" spans="1:4" ht="22" customHeight="1">
-      <c r="A123" s="21"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="3"/>
-      <c r="D123" s="17"/>
-    </row>
-    <row r="124" spans="1:4" ht="22" customHeight="1">
-      <c r="A124" s="21"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="3"/>
-      <c r="D124" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2178,7 +2122,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161EE746-A892-B540-AEC4-9A620491759C}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1">
@@ -2298,16 +2242,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" style="5" customWidth="1"/>
     <col min="2" max="2" width="48" style="5" customWidth="1"/>
     <col min="3" max="3" width="14" style="5" customWidth="1"/>
-    <col min="4" max="4" width="52.33203125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="8.83203125" style="5"/>
+    <col min="4" max="4" width="52.375" style="5" customWidth="1"/>
+    <col min="5" max="16384" width="8.875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="28" t="s">
         <v>3</v>
       </c>
@@ -2315,7 +2259,7 @@
       <c r="C1" s="28"/>
       <c r="D1" s="28"/>
     </row>
-    <row r="2" spans="1:4" ht="17">
+    <row r="2" spans="1:4" ht="15.75">
       <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
@@ -2329,7 +2273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="19">
+    <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="9" t="s">
         <v>9</v>
       </c>
@@ -2343,7 +2287,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.5" customHeight="1">
+    <row r="4" spans="1:4" ht="14.45" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -2357,7 +2301,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="17">
+    <row r="5" spans="1:4">
       <c r="A5" s="13" t="s">
         <v>14</v>
       </c>
@@ -2377,5 +2321,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>